--- a/assets/docs/lop2/Dao duc - Lop 2.xlsx
+++ b/assets/docs/lop2/Dao duc - Lop 2.xlsx
@@ -938,7 +938,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Chiếu các cách ứng xử trên màn hình cho HS chọn cách đúng gồm nhận lỗi, xin lỗi, sửa lỗi.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Nhận lỗi và sửa lỗi”, GV chiếu các đoạn phim tình huống ngắn về bạn nhỏ làm hỏng đồ của bạn, quên làm bài, nói dối mẹ
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các cách ứng xử trên màn hình cho HS chọn cách đúng gồm nhận lỗi, xin lỗi, sửa lỗi; máy báo đúng
 KNS: KN tự nhận thức: dám nhận lỗi và sửa lỗi; chịu trách nhiệm về việc mình làm.</t>
         </is>
       </c>
